--- a/data/trending_integrated_20260916_15.xlsx
+++ b/data/trending_integrated_20260916_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G2" t="n">
-        <v>1249</v>
+        <v>1264</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7500409410</v>
+        <v>7507739970</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13520</v>
+        <v>13660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.36%</t>
+          <t>'+27.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
         <v>112</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>181039792155</v>
+        <v>182182493590</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16090</v>
+        <v>16030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.79%</t>
+          <t>'+13.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F4" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G4" t="n">
-        <v>2178</v>
+        <v>2241</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>638802608285</v>
+        <v>648137518910</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인/기관 대량 순매수, 미국 자회사 대규모 광통신 수주 기대감. 10만원 이상 상승 전망하며 긍정적 논조.</t>
+          <t>삼성과의 4381억 공급 계약 및 미국 자회사 인캡의 대규모 광통신 수주 가능성, 외국인/기관 600억 대량 순매수 등 긍정적인 사실 기반의 호재가 다수 확인됨. 주가 상승에 대한 기대감이 높음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수주', '순매수', '광통신']</t>
+          <t>['공급 계약', '광통신 수주', '외국인 순매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4350</v>
+        <v>4380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.58%</t>
+          <t>'+6.31%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>322011057073</v>
+        <v>323510800751</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4725</v>
+        <v>4685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.00%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H6" t="n">
         <v>1.66</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>130486400658</v>
+        <v>131913892626</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -1023,11 +1023,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194200</v>
+        <v>1754000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1035,19 +1035,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>455</v>
       </c>
       <c r="G7" t="n">
-        <v>365</v>
+        <v>1877</v>
       </c>
       <c r="H7" t="n">
-        <v>75.66</v>
+        <v>50.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,130 +1055,130 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>187100</v>
+        <v>1690000</v>
       </c>
       <c r="K7" t="n">
-        <v>187200</v>
+        <v>1686000</v>
       </c>
       <c r="L7" t="n">
-        <v>195900</v>
+        <v>1755000</v>
       </c>
       <c r="M7" t="n">
-        <v>186100</v>
+        <v>1686000</v>
       </c>
       <c r="N7" t="n">
-        <v>75.67</v>
+        <v>50.27</v>
       </c>
       <c r="O7" t="n">
-        <v>595515131200</v>
+        <v>4081575210000</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>61800</v>
+        <v>331500</v>
       </c>
       <c r="R7" t="n">
-        <v>-146000</v>
+        <v>-16000</v>
       </c>
       <c r="S7" t="n">
-        <v>16000</v>
+        <v>125000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>SK하이닉스의 미국 내 메모리 반도체 생산 관련 인텔과의 협상 소식이 있으며, 외국인 선물 매수세 유입 및 자사주 매입 진행으로 주가 상승 기대감이 존재함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['메모리 반도체', '인텔', '자사주 매입']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7150</v>
+        <v>193000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.62%</t>
+          <t>'+3.15%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>372</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>75.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6900</v>
+        <v>187100</v>
       </c>
       <c r="K8" t="n">
-        <v>6770</v>
+        <v>187200</v>
       </c>
       <c r="L8" t="n">
-        <v>8590</v>
+        <v>195900</v>
       </c>
       <c r="M8" t="n">
-        <v>6660</v>
+        <v>186100</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>75.67</v>
       </c>
       <c r="O8" t="n">
-        <v>81537314290</v>
+        <v>622832049050</v>
       </c>
       <c r="P8" t="n">
-        <v>10360</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>2965</v>
+        <v>61800</v>
       </c>
       <c r="R8" t="n">
-        <v>87000</v>
+        <v>-146000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,99 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1744000</v>
+        <v>7100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+2.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>458</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>1850</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>50.2</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1690000</v>
+        <v>6900</v>
       </c>
       <c r="K9" t="n">
-        <v>1686000</v>
+        <v>6770</v>
       </c>
       <c r="L9" t="n">
-        <v>1750000</v>
+        <v>8590</v>
       </c>
       <c r="M9" t="n">
-        <v>1686000</v>
+        <v>6660</v>
       </c>
       <c r="N9" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3889319954500</v>
+        <v>81714553465</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q9" t="n">
-        <v>331500</v>
+        <v>2965</v>
       </c>
       <c r="R9" t="n">
-        <v>-16000</v>
+        <v>87000</v>
       </c>
       <c r="S9" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 인텔과 미국 내 메모리 반도체 생산 협상 진행 중. 외국인 선물 매수 유입.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['인텔', '메모리 반도체', '미국 생산']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13590</v>
+        <v>13640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.18%</t>
+          <t>'+2.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>18631789080</v>
+        <v>19221198790</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252500</v>
+        <v>253000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+1.81%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G11" t="n">
-        <v>1523</v>
+        <v>1565</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2343103606500</v>
+        <v>2415663512500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 다양한 의견이 혼재하나, 주가 상승 기대감과 관련된 구체적인 근거는 부족함.</t>
+          <t>정치 관련 언급이 주를 이루며, 금리 인상 및 미국 경제 관련 불확실성이 혼재되어 있음. 주가 전망은 긍정적 언급도 있으나 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['금리 인상', 'FOMC', '총선']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5290</v>
+        <v>3380</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.15%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.39</v>
+        <v>-1.34</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="H12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5230</v>
+        <v>3360</v>
       </c>
       <c r="K12" t="n">
-        <v>5750</v>
+        <v>3570</v>
       </c>
       <c r="L12" t="n">
-        <v>5880</v>
+        <v>3910</v>
       </c>
       <c r="M12" t="n">
-        <v>5020</v>
+        <v>3215</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>1.34</v>
       </c>
       <c r="O12" t="n">
-        <v>66561004560</v>
+        <v>109702306381</v>
       </c>
       <c r="P12" t="n">
-        <v>8980</v>
+        <v>5100</v>
       </c>
       <c r="Q12" t="n">
-        <v>2795</v>
+        <v>966</v>
       </c>
       <c r="R12" t="n">
-        <v>88000</v>
+        <v>-25000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '독점']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3525</v>
+        <v>5250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>-1.39</v>
       </c>
       <c r="E13" t="n">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>659</v>
+        <v>217</v>
       </c>
       <c r="H13" t="n">
-        <v>3.11</v>
+        <v>1.29</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3515</v>
+        <v>5230</v>
       </c>
       <c r="K13" t="n">
-        <v>4120</v>
+        <v>5750</v>
       </c>
       <c r="L13" t="n">
-        <v>4140</v>
+        <v>5880</v>
       </c>
       <c r="M13" t="n">
-        <v>3410</v>
+        <v>5020</v>
       </c>
       <c r="N13" t="n">
-        <v>3.16</v>
+        <v>2.68</v>
       </c>
       <c r="O13" t="n">
-        <v>20908749761</v>
+        <v>67138302925</v>
       </c>
       <c r="P13" t="n">
-        <v>16110</v>
+        <v>8980</v>
       </c>
       <c r="Q13" t="n">
-        <v>2300</v>
+        <v>2795</v>
       </c>
       <c r="R13" t="n">
-        <v>-341000</v>
+        <v>88000</v>
       </c>
       <c r="S13" t="n">
-        <v>-313000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
+          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['양자보안', '사이버보안', '독점']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10060</v>
+        <v>10050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H14" t="n">
         <v>0.67</v>
@@ -1714,7 +1714,7 @@
         <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>119979561985</v>
+        <v>120555868925</v>
       </c>
       <c r="P14" t="n">
         <v>15960</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 내년 1분기 국내 도입 공식화 전망. 재료 소멸 논란 속 기대감 존재.</t>
+          <t>내년 초 미프진 도입 관련 소식과 함께 주가 상승 기대감이 있으나, 재료 소멸 및 주가 하락에 대한 우려도 공존함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3320</v>
+        <v>3460</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.19%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.34</v>
+        <v>-0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
-        <v>238</v>
+        <v>663</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3360</v>
+        <v>3515</v>
       </c>
       <c r="K15" t="n">
-        <v>3570</v>
+        <v>4120</v>
       </c>
       <c r="L15" t="n">
-        <v>3910</v>
+        <v>4140</v>
       </c>
       <c r="M15" t="n">
-        <v>3215</v>
+        <v>3410</v>
       </c>
       <c r="N15" t="n">
-        <v>1.34</v>
+        <v>3.16</v>
       </c>
       <c r="O15" t="n">
-        <v>108834818933</v>
+        <v>21122214124</v>
       </c>
       <c r="P15" t="n">
-        <v>5100</v>
+        <v>16110</v>
       </c>
       <c r="Q15" t="n">
-        <v>966</v>
+        <v>2300</v>
       </c>
       <c r="R15" t="n">
-        <v>-25000</v>
+        <v>-341000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-313000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,20 +1831,20 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31950</v>
+        <v>31900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F16" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G16" t="n">
-        <v>1241</v>
+        <v>1262</v>
       </c>
       <c r="H16" t="n">
         <v>17.16</v>
@@ -1898,7 +1898,7 @@
         <v>17.5</v>
       </c>
       <c r="O16" t="n">
-        <v>10088240750</v>
+        <v>10234703950</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1958,13 +1958,13 @@
         <v>-0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="H17" t="n">
         <v>26.66</v>
@@ -1990,7 +1990,7 @@
         <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>15779786220</v>
+        <v>16361857135</v>
       </c>
       <c r="P17" t="n">
         <v>17950</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>LG디스플레이, PBR 0.6배 수준. 개인 주주 손실 누적 및 경영진 성과급 논란.</t>
+          <t>삼성디스플레이와의 비교 언급 및 FLiPP 양산에 대한 기대감도 있으나, 낮은 PBR, 개인 주주들의 손실, 경영진 성과급 문제 등 부정적인 내용이 주를 이루며 주가 하락에 대한 우려가 큼.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['PBR', '개인 주주', '경영진']</t>
+          <t>['PBR', 'FLiPP', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10450</v>
+        <v>20200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.29</v>
+        <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="G18" t="n">
-        <v>197</v>
+        <v>410</v>
       </c>
       <c r="H18" t="n">
-        <v>19.22</v>
+        <v>28.51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10660</v>
+        <v>20700</v>
       </c>
       <c r="K18" t="n">
-        <v>10500</v>
+        <v>20750</v>
       </c>
       <c r="L18" t="n">
-        <v>10900</v>
+        <v>20750</v>
       </c>
       <c r="M18" t="n">
-        <v>10060</v>
+        <v>20150</v>
       </c>
       <c r="N18" t="n">
-        <v>17.93</v>
+        <v>28.9</v>
       </c>
       <c r="O18" t="n">
-        <v>120934133380</v>
+        <v>39032140450</v>
       </c>
       <c r="P18" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q18" t="n">
-        <v>1760</v>
+        <v>18440</v>
       </c>
       <c r="R18" t="n">
-        <v>-467000</v>
+        <v>-1014000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>-65000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
+          <t>LNG선 등 1.6조 수주 소식과 IBK증권의 목표주가 상향 조정 리포트가 있으나, 정치적 언급 및 주가 하락세, 공매도 관련 부정적 의견이 다수 존재함.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['연기금', '순매수', '투주']</t>
+          <t>['LNG선 수주', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,43 +2115,43 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20200</v>
+        <v>10360</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.39</v>
+        <v>1.29</v>
       </c>
       <c r="E19" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="F19" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G19" t="n">
-        <v>399</v>
+        <v>196</v>
       </c>
       <c r="H19" t="n">
-        <v>28.51</v>
+        <v>19.22</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>20700</v>
+        <v>10660</v>
       </c>
       <c r="K19" t="n">
-        <v>20750</v>
+        <v>10500</v>
       </c>
       <c r="L19" t="n">
-        <v>20750</v>
+        <v>10900</v>
       </c>
       <c r="M19" t="n">
-        <v>20150</v>
+        <v>10060</v>
       </c>
       <c r="N19" t="n">
-        <v>28.9</v>
+        <v>17.93</v>
       </c>
       <c r="O19" t="n">
-        <v>37545256900</v>
+        <v>121860920305</v>
       </c>
       <c r="P19" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q19" t="n">
-        <v>18440</v>
+        <v>1760</v>
       </c>
       <c r="R19" t="n">
-        <v>-1014000</v>
+        <v>-467000</v>
       </c>
       <c r="S19" t="n">
-        <v>-65000</v>
+        <v>2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.6조 규모의 LNG선 수주 공시가 있으나, 목표치 초과 달성에 대한 긍정적 평가와 함께 IBK투자증권의 목표주가 상향 리포트도 존재. 다만, 주가 하락 및 공매도에 대한 부정적 정서가 강하게 나타남.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LNG선', '수주', '공매도']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,43 +2207,43 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18600</v>
+        <v>83700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.90%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>125</v>
+        <v>337</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="G20" t="n">
-        <v>462</v>
+        <v>1085</v>
       </c>
       <c r="H20" t="n">
-        <v>10.64</v>
+        <v>23.37</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>19130</v>
+        <v>86200</v>
       </c>
       <c r="K20" t="n">
-        <v>19160</v>
+        <v>86200</v>
       </c>
       <c r="L20" t="n">
-        <v>19340</v>
+        <v>86300</v>
       </c>
       <c r="M20" t="n">
-        <v>18330</v>
+        <v>83500</v>
       </c>
       <c r="N20" t="n">
-        <v>10.53</v>
+        <v>23.45</v>
       </c>
       <c r="O20" t="n">
-        <v>62146851285</v>
+        <v>158680291900</v>
       </c>
       <c r="P20" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-59000</v>
+        <v>-140000</v>
       </c>
       <c r="S20" t="n">
-        <v>-140000</v>
+        <v>-123000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 대차 해지 운동 참여 독려. 대형 계약 임박 기대감 있으나 구체적 근거 제시 미흡.</t>
+          <t>웨스팅하우스 지분 인수 및 경영권 참여 기대감 속에서 대미 투자 관련 단독 뉴스가 언급됨. 하지만 공매도 세력의 움직임과 투자 연기 가능성 등 부정적 요인도 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['대차해지', '주가조작', '계약']</t>
+          <t>['웨스팅하우스', '지분 인수', '대미 투자']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83750</v>
+        <v>18570</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.84%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.08</v>
+        <v>0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>332</v>
+        <v>127</v>
       </c>
       <c r="F21" t="n">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="G21" t="n">
-        <v>1078</v>
+        <v>478</v>
       </c>
       <c r="H21" t="n">
-        <v>23.37</v>
+        <v>10.64</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>86200</v>
+        <v>19130</v>
       </c>
       <c r="K21" t="n">
-        <v>86200</v>
+        <v>19160</v>
       </c>
       <c r="L21" t="n">
-        <v>86300</v>
+        <v>19340</v>
       </c>
       <c r="M21" t="n">
-        <v>83500</v>
+        <v>18330</v>
       </c>
       <c r="N21" t="n">
-        <v>23.45</v>
+        <v>10.53</v>
       </c>
       <c r="O21" t="n">
-        <v>153731045250</v>
+        <v>64070023435</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="S21" t="n">
         <v>-140000</v>
       </c>
-      <c r="S21" t="n">
-        <v>-123000</v>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대와 대미 투자 연기 이슈 혼재. 공매도 세력의 압박.</t>
+          <t>대차 해지 운동 참여 독려와 함께 주가 10만원 이상 상승 전망 언급. 대형 계약 임박 기대감도 있으나, 주가 조작 의혹 제기 및 부정적 언급도 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분인수', '대미투자']</t>
+          <t>['대차 해지', '주가 조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16950</v>
+        <v>17010</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F22" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G22" t="n">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H22" t="n">
         <v>0.45</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>161713336130</v>
+        <v>162246642485</v>
       </c>
       <c r="P22" t="n">
         <v>30550</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 보안주 동반 상승 영향. 개미 털기 의혹 및 22,000원 목표가 제시.</t>
+          <t>미국 보안주 동반 상승 및 상용화, 매출 발생 가능성에 대한 기대감이 있으나, 주가 인위적 하락 및 개미 털기 의혹, 수급 쏠림 현상 등 부정적인 분석도 존재함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['보안주', '개미 털기', '목표가']</t>
+          <t>['보안주', '상용화', '매출 발생']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6000</v>
+        <v>6030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-4.44%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>53091269060</v>
+        <v>53927012250</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13980</v>
+        <v>13950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.68%</t>
+          <t>'-6.88%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F24" t="n">
         <v>132</v>
       </c>
       <c r="G24" t="n">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>36987917940</v>
+        <v>37286210710</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>

--- a/data/trending_integrated_20260916_15.xlsx
+++ b/data/trending_integrated_20260916_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>1264</v>
+        <v>1285</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7507739970</v>
+        <v>7512920130</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오의 미투온 인수 가능성 제기. 합법 카지노 사업 확장 기대감과 공매도 숏스퀴즈 전망.</t>
+          <t>카카오 인수 관련 기대감과 공매도 숏스퀴즈 가능성 언급. 본느 7연상 기록 경신 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오', '인수', '공매도 숏스퀴즈']</t>
+          <t>['카카오 인수', '공매도', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13660</v>
+        <v>13630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.66%</t>
+          <t>'+27.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
         <v>112</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>182182493590</v>
+        <v>183152160860</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16030</v>
+        <v>16060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.37%</t>
+          <t>'+13.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F4" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G4" t="n">
-        <v>2241</v>
+        <v>2317</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>648137518910</v>
+        <v>656181999585</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성과의 4381억 공급 계약 및 미국 자회사 인캡의 대규모 광통신 수주 가능성, 외국인/기관 600억 대량 순매수 등 긍정적인 사실 기반의 호재가 다수 확인됨. 주가 상승에 대한 기대감이 높음.</t>
+          <t>삼성과 4381억 규모 공급 계약 체결 및 외인/기관 대량 순매수. 미국 자회사 대규모 수주 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급 계약', '광통신 수주', '외국인 순매수']</t>
+          <t>['공급 계약', '순매수', '대량 수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4380</v>
+        <v>4415</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.31%</t>
+          <t>'+7.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G5" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>323510800751</v>
+        <v>325751161954</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 미증시 상승 영향 및 4천원 지지선 언급. 단기 차익 실현 기대.</t>
+          <t>광케이블 관련 미장 상승 및 4천원 지지선 언급. 단차 차익 및 알고리즘 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '미증시', '지지선']</t>
+          <t>['광케이블', '지지선', '단차']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4685</v>
+        <v>4700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+4.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>131913892626</v>
+        <v>132519653869</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1754000</v>
+        <v>1759000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.79%</t>
+          <t>'+4.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G7" t="n">
-        <v>1877</v>
+        <v>1925</v>
       </c>
       <c r="H7" t="n">
         <v>50.2</v>
@@ -1061,7 +1061,7 @@
         <v>1686000</v>
       </c>
       <c r="L7" t="n">
-        <v>1755000</v>
+        <v>1760000</v>
       </c>
       <c r="M7" t="n">
         <v>1686000</v>
@@ -1070,7 +1070,7 @@
         <v>50.27</v>
       </c>
       <c r="O7" t="n">
-        <v>4081575210000</v>
+        <v>4235556305500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스의 미국 내 메모리 반도체 생산 관련 인텔과의 협상 소식이 있으며, 외국인 선물 매수세 유입 및 자사주 매입 진행으로 주가 상승 기대감이 존재함.</t>
+          <t>SK하이닉스, 인텔과 미국 내 메모리 생산 방안 논의 중. 외인 선물 1조 매수 등 긍정적 수급과 함께 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['메모리 반도체', '인텔', '자사주 매입']</t>
+          <t>['HBM', 'TSV', '인텔']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193000</v>
+        <v>7180</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.15%</t>
+          <t>'+4.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>372</v>
+        <v>70</v>
       </c>
       <c r="H8" t="n">
-        <v>75.66</v>
+        <v>0.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>187100</v>
+        <v>6900</v>
       </c>
       <c r="K8" t="n">
-        <v>187200</v>
+        <v>6770</v>
       </c>
       <c r="L8" t="n">
-        <v>195900</v>
+        <v>8590</v>
       </c>
       <c r="M8" t="n">
-        <v>186100</v>
+        <v>6660</v>
       </c>
       <c r="N8" t="n">
-        <v>75.67</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>622832049050</v>
+        <v>82199345900</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>10360</v>
       </c>
       <c r="Q8" t="n">
-        <v>61800</v>
+        <v>2965</v>
       </c>
       <c r="R8" t="n">
-        <v>-146000</v>
+        <v>87000</v>
       </c>
       <c r="S8" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7100</v>
+        <v>194000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.90%</t>
+          <t>'+3.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>376</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>75.66</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6900</v>
+        <v>187100</v>
       </c>
       <c r="K9" t="n">
-        <v>6770</v>
+        <v>187200</v>
       </c>
       <c r="L9" t="n">
-        <v>8590</v>
+        <v>195900</v>
       </c>
       <c r="M9" t="n">
-        <v>6660</v>
+        <v>186100</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>75.67</v>
       </c>
       <c r="O9" t="n">
-        <v>81714553465</v>
+        <v>641422838850</v>
       </c>
       <c r="P9" t="n">
-        <v>10360</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>2965</v>
+        <v>61800</v>
       </c>
       <c r="R9" t="n">
-        <v>87000</v>
+        <v>-146000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13640</v>
+        <v>13610</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.56%</t>
+          <t>'+2.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>19221198790</v>
+        <v>19517747240</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253000</v>
+        <v>253250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.81%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G11" t="n">
-        <v>1565</v>
+        <v>1634</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2415663512500</v>
+        <v>2498035754250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치 관련 언급이 주를 이루며, 금리 인상 및 미국 경제 관련 불확실성이 혼재되어 있음. 주가 전망은 긍정적 언급도 있으나 구체적인 근거는 부족함.</t>
+          <t>정치적 이슈와 금리 인상 관련 언급이 다수. 연말 최고점 돌파 기대 및 이재용 구속 관련 부정적 논조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리 인상', 'FOMC', '총선']</t>
+          <t>['금리 인상', '정치 이슈', '이재용']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3380</v>
+        <v>5280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'+0.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.34</v>
+        <v>-1.39</v>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3360</v>
+        <v>5230</v>
       </c>
       <c r="K12" t="n">
-        <v>3570</v>
+        <v>5750</v>
       </c>
       <c r="L12" t="n">
-        <v>3910</v>
+        <v>5880</v>
       </c>
       <c r="M12" t="n">
-        <v>3215</v>
+        <v>5020</v>
       </c>
       <c r="N12" t="n">
-        <v>1.34</v>
+        <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>109702306381</v>
+        <v>67507780590</v>
       </c>
       <c r="P12" t="n">
-        <v>5100</v>
+        <v>8980</v>
       </c>
       <c r="Q12" t="n">
-        <v>966</v>
+        <v>2795</v>
       </c>
       <c r="R12" t="n">
-        <v>-25000</v>
+        <v>88000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
+          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '트럼프']</t>
+          <t>['양자보안', '사이버보안', '독점']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한컴위드</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5250</v>
+        <v>3380</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.39</v>
+        <v>-1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="H13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5230</v>
+        <v>3360</v>
       </c>
       <c r="K13" t="n">
-        <v>5750</v>
+        <v>3570</v>
       </c>
       <c r="L13" t="n">
-        <v>5880</v>
+        <v>3910</v>
       </c>
       <c r="M13" t="n">
-        <v>5020</v>
+        <v>3215</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>1.34</v>
       </c>
       <c r="O13" t="n">
-        <v>67138302925</v>
+        <v>110296487466</v>
       </c>
       <c r="P13" t="n">
-        <v>8980</v>
+        <v>5100</v>
       </c>
       <c r="Q13" t="n">
-        <v>2795</v>
+        <v>966</v>
       </c>
       <c r="R13" t="n">
-        <v>88000</v>
+        <v>-25000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 사이버보안주 강세 속 양자보안 구축 의무화 및 3기업 독점 관련 기대.</t>
+          <t>양자내성암호, 양자보안 관련 트럼프 행정명령 수혜 기대. 대한광통신과 유사한 흐름.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['양자보안', '사이버보안', '독점']</t>
+          <t>['양자암호', '보안', '트럼프']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>054920</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10050</v>
+        <v>3535</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'+0.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>318</v>
+        <v>665</v>
       </c>
       <c r="H14" t="n">
-        <v>0.67</v>
+        <v>3.11</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10120</v>
+        <v>3515</v>
       </c>
       <c r="K14" t="n">
-        <v>10190</v>
+        <v>4120</v>
       </c>
       <c r="L14" t="n">
-        <v>10920</v>
+        <v>4140</v>
       </c>
       <c r="M14" t="n">
-        <v>9790</v>
+        <v>3410</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>120555868925</v>
+        <v>21338991892</v>
       </c>
       <c r="P14" t="n">
-        <v>15960</v>
+        <v>16110</v>
       </c>
       <c r="Q14" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R14" t="n">
-        <v>-21000</v>
+        <v>-341000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-313000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>내년 초 미프진 도입 관련 소식과 함께 주가 상승 기대감이 있으나, 재료 소멸 및 주가 하락에 대한 우려도 공존함.</t>
+          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미프진', '독점 공급', '재료 소멸']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3460</v>
+        <v>10000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.19%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>663</v>
+        <v>324</v>
       </c>
       <c r="H15" t="n">
-        <v>3.11</v>
+        <v>0.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3515</v>
+        <v>10120</v>
       </c>
       <c r="K15" t="n">
-        <v>4120</v>
+        <v>10190</v>
       </c>
       <c r="L15" t="n">
-        <v>4140</v>
+        <v>10920</v>
       </c>
       <c r="M15" t="n">
-        <v>3410</v>
+        <v>9790</v>
       </c>
       <c r="N15" t="n">
-        <v>3.16</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>21122214124</v>
+        <v>122793451565</v>
       </c>
       <c r="P15" t="n">
-        <v>16110</v>
+        <v>15960</v>
       </c>
       <c r="Q15" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="R15" t="n">
-        <v>-341000</v>
+        <v>-21000</v>
       </c>
       <c r="S15" t="n">
-        <v>-313000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
+          <t>미프진 독점 공급 관련 기대감과 재료 소멸 논란 속 주가 변동성. 내년 1분기 도입 및 PR 확산 시 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['미프진', '독점 공급', '주가 변동성']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31900</v>
+        <v>31850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.34</v>
       </c>
       <c r="E16" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F16" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G16" t="n">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="H16" t="n">
         <v>17.16</v>
@@ -1898,7 +1898,7 @@
         <v>17.5</v>
       </c>
       <c r="O16" t="n">
-        <v>10234703950</v>
+        <v>10466808800</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1958,13 +1958,13 @@
         <v>-0.5</v>
       </c>
       <c r="E17" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="H17" t="n">
         <v>26.66</v>
@@ -1990,7 +1990,7 @@
         <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>16361857135</v>
+        <v>16786734650</v>
       </c>
       <c r="P17" t="n">
         <v>17950</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼성디스플레이와의 비교 언급 및 FLiPP 양산에 대한 기대감도 있으나, 낮은 PBR, 개인 주주들의 손실, 경영진 성과급 문제 등 부정적인 내용이 주를 이루며 주가 하락에 대한 우려가 큼.</t>
+          <t>저조한 PBR과 주주 총 손실 언급. 삼성디스플레이 대비 낮은 가치평가와 경영진 성과급 논란.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['PBR', 'FLiPP', '실적']</t>
+          <t>['PBR', '가치평가', '경영진']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20200</v>
+        <v>20250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F18" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G18" t="n">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="H18" t="n">
         <v>28.51</v>
@@ -2082,7 +2082,7 @@
         <v>28.9</v>
       </c>
       <c r="O18" t="n">
-        <v>39032140450</v>
+        <v>40891988775</v>
       </c>
       <c r="P18" t="n">
         <v>35350</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10360</v>
+        <v>10380</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.63%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1.29</v>
       </c>
       <c r="E19" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F19" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G19" t="n">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="H19" t="n">
         <v>19.22</v>
@@ -2174,7 +2174,7 @@
         <v>17.93</v>
       </c>
       <c r="O19" t="n">
-        <v>121860920305</v>
+        <v>123226010610</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2234,13 +2234,13 @@
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="F20" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G20" t="n">
-        <v>1085</v>
+        <v>1095</v>
       </c>
       <c r="H20" t="n">
         <v>23.37</v>
@@ -2266,7 +2266,7 @@
         <v>23.45</v>
       </c>
       <c r="O20" t="n">
-        <v>158680291900</v>
+        <v>168176311650</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18570</v>
+        <v>17040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.93%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="F21" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="G21" t="n">
-        <v>478</v>
+        <v>366</v>
       </c>
       <c r="H21" t="n">
-        <v>10.64</v>
+        <v>0.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19130</v>
+        <v>17550</v>
       </c>
       <c r="K21" t="n">
-        <v>19160</v>
+        <v>17150</v>
       </c>
       <c r="L21" t="n">
-        <v>19340</v>
+        <v>18860</v>
       </c>
       <c r="M21" t="n">
-        <v>18330</v>
+        <v>16710</v>
       </c>
       <c r="N21" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="O21" t="n">
-        <v>64070023435</v>
+        <v>162932021345</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R21" t="n">
-        <v>-59000</v>
+        <v>-12000</v>
       </c>
       <c r="S21" t="n">
-        <v>-140000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>대차 해지 운동 참여 독려와 함께 주가 10만원 이상 상승 전망 언급. 대형 계약 임박 기대감도 있으나, 주가 조작 의혹 제기 및 부정적 언급도 혼재.</t>
+          <t>미국 보안주 상승 및 상용화, 매출 발생 기업 언급. 개미 털기 의혹 및 22,000원 목표 가격 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['대차 해지', '주가 조작', '대형 계약']</t>
+          <t>['보안주', '상용화', '매출 발생']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17010</v>
+        <v>18570</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="F22" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>367</v>
+        <v>483</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45</v>
+        <v>10.64</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17550</v>
+        <v>19130</v>
       </c>
       <c r="K22" t="n">
-        <v>17150</v>
+        <v>19160</v>
       </c>
       <c r="L22" t="n">
-        <v>18860</v>
+        <v>19340</v>
       </c>
       <c r="M22" t="n">
-        <v>16710</v>
+        <v>18330</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>10.53</v>
       </c>
       <c r="O22" t="n">
-        <v>162246642485</v>
+        <v>69812532240</v>
       </c>
       <c r="P22" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q22" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-12000</v>
+        <v>-59000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 보안주 동반 상승 및 상용화, 매출 발생 가능성에 대한 기대감이 있으나, 주가 인위적 하락 및 개미 털기 의혹, 수급 쏠림 현상 등 부정적인 분석도 존재함.</t>
+          <t>대차 해지 운동 참여 독려와 함께 주가 10만원 이상 상승 전망 언급. 대형 계약 임박 기대감도 있으나, 주가 조작 의혹 제기 및 부정적 언급도 혼재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['보안주', '상용화', '매출 발생']</t>
+          <t>['대차 해지', '주가 조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6030</v>
+        <v>6050</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.44%</t>
+          <t>'-4.12%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>53927012250</v>
+        <v>54572992630</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13950</v>
+        <v>14050</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.88%</t>
+          <t>'-6.21%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F24" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G24" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>37286210710</v>
+        <v>37817227170</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>

--- a/data/trending_integrated_20260916_15.xlsx
+++ b/data/trending_integrated_20260916_15.xlsx
@@ -581,10 +581,10 @@
         <v>329</v>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G2" t="n">
-        <v>1285</v>
+        <v>1294</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7512920130</v>
+        <v>7514959170</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13630</v>
+        <v>13530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.38%</t>
+          <t>'+26.45%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>183152160860</v>
+        <v>183705375500</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16060</v>
+        <v>16100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.58%</t>
+          <t>'+13.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G4" t="n">
-        <v>2317</v>
+        <v>2363</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>656181999585</v>
+        <v>659050697585</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성과 4381억 규모 공급 계약 체결 및 외인/기관 대량 순매수. 미국 자회사 대규모 수주 기대감.</t>
+          <t>외국인/기관 600억 대량 순매수 및 미국 자회사 대규모 광통신 수주 기대감으로 인한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급 계약', '순매수', '대량 수주']</t>
+          <t>['대량 순매수', '광통신 수주', '외인 기관']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4415</v>
+        <v>4410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.16%</t>
+          <t>'+7.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G5" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>325751161954</v>
+        <v>326217347464</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4700</v>
+        <v>4725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.44%</t>
+          <t>'+5.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F6" t="n">
         <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H6" t="n">
         <v>1.66</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>132519653869</v>
+        <v>132734532694</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -1044,7 +1044,7 @@
         <v>456</v>
       </c>
       <c r="G7" t="n">
-        <v>1925</v>
+        <v>1904</v>
       </c>
       <c r="H7" t="n">
         <v>50.2</v>
@@ -1070,7 +1070,7 @@
         <v>50.27</v>
       </c>
       <c r="O7" t="n">
-        <v>4235556305500</v>
+        <v>4690750325500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스, 인텔과 미국 내 메모리 생산 방안 논의 중. 외인 선물 1조 매수 등 긍정적 수급과 함께 주가 상승 기대.</t>
+          <t>인텔과의 미국 내 메모리 생산 방안 논의 뉴스 기반 외국인 및 기관 매수세 유입, 단기 변동성 확대 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['HBM', 'TSV', '인텔']</t>
+          <t>['인텔', '메모리 생산', '외인 기관 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7180</v>
+        <v>194600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.06%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>70</v>
+        <v>386</v>
       </c>
       <c r="H8" t="n">
-        <v>0.79</v>
+        <v>75.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6900</v>
+        <v>187100</v>
       </c>
       <c r="K8" t="n">
-        <v>6770</v>
+        <v>187200</v>
       </c>
       <c r="L8" t="n">
-        <v>8590</v>
+        <v>195900</v>
       </c>
       <c r="M8" t="n">
-        <v>6660</v>
+        <v>186100</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>75.67</v>
       </c>
       <c r="O8" t="n">
-        <v>82199345900</v>
+        <v>674449183250</v>
       </c>
       <c r="P8" t="n">
-        <v>10360</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>2965</v>
+        <v>61800</v>
       </c>
       <c r="R8" t="n">
-        <v>87000</v>
+        <v>-146000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
+          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '대장주']</t>
+          <t>['우선주', '배당', '괴리율']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194000</v>
+        <v>7160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.69%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>376</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>75.66</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>187100</v>
+        <v>6900</v>
       </c>
       <c r="K9" t="n">
-        <v>187200</v>
+        <v>6770</v>
       </c>
       <c r="L9" t="n">
-        <v>195900</v>
+        <v>8590</v>
       </c>
       <c r="M9" t="n">
-        <v>186100</v>
+        <v>6660</v>
       </c>
       <c r="N9" t="n">
-        <v>75.67</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>641422838850</v>
+        <v>82472048820</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>10360</v>
       </c>
       <c r="Q9" t="n">
-        <v>61800</v>
+        <v>2965</v>
       </c>
       <c r="R9" t="n">
-        <v>-146000</v>
+        <v>87000</v>
       </c>
       <c r="S9" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 배당 관련 긍정적 기대감, 본주와의 괴리율 축소 전망.</t>
+          <t>보안 대장주로서의 지위 강조 및 AI 관련 논의 언급. 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우선주', '배당', '괴리율']</t>
+          <t>['보안주', 'AI', '대장주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13610</v>
+        <v>13630</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.33%</t>
+          <t>'+2.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>19517747240</v>
+        <v>19687617930</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253250</v>
+        <v>253500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G11" t="n">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2498035754250</v>
+        <v>2819090715750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 금리 인상 관련 언급이 다수. 연말 최고점 돌파 기대 및 이재용 구속 관련 부정적 논조.</t>
+          <t>정치적 이슈에 대한 언급이 주를 이루며, 경제 전망에 대한 직접적인 내용은 부재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['금리 인상', '정치 이슈', '이재용']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5280</v>
+        <v>5290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.15%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-1.39</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H12" t="n">
         <v>1.29</v>
@@ -1530,7 +1530,7 @@
         <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>67507780590</v>
+        <v>67793488200</v>
       </c>
       <c r="P12" t="n">
         <v>8980</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3380</v>
+        <v>3375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F13" t="n">
         <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>1.34</v>
       </c>
       <c r="O13" t="n">
-        <v>110296487466</v>
+        <v>110453421591</v>
       </c>
       <c r="P13" t="n">
         <v>5100</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3535</v>
+        <v>3520</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.57%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="H14" t="n">
         <v>3.11</v>
@@ -1714,7 +1714,7 @@
         <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>21338991892</v>
+        <v>21571026772</v>
       </c>
       <c r="P14" t="n">
         <v>16110</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10000</v>
+        <v>9970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.19%</t>
+          <t>'-1.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F15" t="n">
         <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H15" t="n">
         <v>0.67</v>
@@ -1806,7 +1806,7 @@
         <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>122793451565</v>
+        <v>123166060375</v>
       </c>
       <c r="P15" t="n">
         <v>15960</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미프진 독점 공급 관련 기대감과 재료 소멸 논란 속 주가 변동성. 내년 1분기 도입 및 PR 확산 시 주가 상승 전망.</t>
+          <t>미프진 관련 재료 소멸 및 도입 시점 불확실성 속에서 주가 변동성 확대 전망. 일부 투자자들은 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['미프진', '독점 공급', '주가 변동성']</t>
+          <t>['미프진', '독점 공급', '재료 소멸']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31850</v>
+        <v>8470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.85%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.34</v>
+        <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>1268</v>
+        <v>547</v>
       </c>
       <c r="H16" t="n">
-        <v>17.16</v>
+        <v>26.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>32450</v>
+        <v>8610</v>
       </c>
       <c r="K16" t="n">
-        <v>32850</v>
+        <v>8600</v>
       </c>
       <c r="L16" t="n">
-        <v>32850</v>
+        <v>8610</v>
       </c>
       <c r="M16" t="n">
-        <v>30900</v>
+        <v>8430</v>
       </c>
       <c r="N16" t="n">
-        <v>17.5</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>10466808800</v>
+        <v>17989169730</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-91000</v>
+        <v>-558000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
+          <t>낮은 PBR에도 불구하고 주가 부진 지속, 개인 투자자들의 손실 누적 및 경영진 성과급 문제 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FDA', '담관암', '신약']</t>
+          <t>['PBR', '개인 손실', '경영진']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>31900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.5</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="G17" t="n">
-        <v>549</v>
+        <v>1280</v>
       </c>
       <c r="H17" t="n">
-        <v>26.66</v>
+        <v>17.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8610</v>
+        <v>32450</v>
       </c>
       <c r="K17" t="n">
-        <v>8600</v>
+        <v>32850</v>
       </c>
       <c r="L17" t="n">
-        <v>8610</v>
+        <v>32850</v>
       </c>
       <c r="M17" t="n">
-        <v>8430</v>
+        <v>30900</v>
       </c>
       <c r="N17" t="n">
-        <v>27.16</v>
+        <v>17.5</v>
       </c>
       <c r="O17" t="n">
-        <v>16786734650</v>
+        <v>10841378600</v>
       </c>
       <c r="P17" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8120</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-558000</v>
+        <v>-91000</v>
       </c>
       <c r="S17" t="n">
-        <v>-58000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>저조한 PBR과 주주 총 손실 언급. 삼성디스플레이 대비 낮은 가치평가와 경영진 성과급 논란.</t>
+          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['PBR', '가치평가', '경영진']</t>
+          <t>['FDA', '담관암', '신약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20250</v>
+        <v>10460</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.39</v>
+        <v>1.29</v>
       </c>
       <c r="E18" t="n">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="F18" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="H18" t="n">
-        <v>28.51</v>
+        <v>19.22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>20700</v>
+        <v>10660</v>
       </c>
       <c r="K18" t="n">
-        <v>20750</v>
+        <v>10500</v>
       </c>
       <c r="L18" t="n">
-        <v>20750</v>
+        <v>10900</v>
       </c>
       <c r="M18" t="n">
-        <v>20150</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="n">
-        <v>28.9</v>
+        <v>17.93</v>
       </c>
       <c r="O18" t="n">
-        <v>40891988775</v>
+        <v>123978325190</v>
       </c>
       <c r="P18" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q18" t="n">
-        <v>18440</v>
+        <v>1760</v>
       </c>
       <c r="R18" t="n">
-        <v>-1014000</v>
+        <v>-467000</v>
       </c>
       <c r="S18" t="n">
-        <v>-65000</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>LNG선 등 1.6조 수주 소식과 IBK증권의 목표주가 상향 조정 리포트가 있으나, 정치적 언급 및 주가 하락세, 공매도 관련 부정적 의견이 다수 존재함.</t>
+          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['LNG선 수주', '목표주가', '공매도']</t>
+          <t>['연기금', '순매수', '투주']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,43 +2115,43 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10380</v>
+        <v>20200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.63%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.29</v>
+        <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>449</v>
       </c>
       <c r="H19" t="n">
-        <v>19.22</v>
+        <v>28.51</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10660</v>
+        <v>20700</v>
       </c>
       <c r="K19" t="n">
-        <v>10500</v>
+        <v>20750</v>
       </c>
       <c r="L19" t="n">
-        <v>10900</v>
+        <v>20750</v>
       </c>
       <c r="M19" t="n">
-        <v>10060</v>
+        <v>20150</v>
       </c>
       <c r="N19" t="n">
-        <v>17.93</v>
+        <v>28.9</v>
       </c>
       <c r="O19" t="n">
-        <v>123226010610</v>
+        <v>45692801575</v>
       </c>
       <c r="P19" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q19" t="n">
-        <v>1760</v>
+        <v>18440</v>
       </c>
       <c r="R19" t="n">
-        <v>-467000</v>
+        <v>-1014000</v>
       </c>
       <c r="S19" t="n">
-        <v>2000</v>
+        <v>-65000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>연기금 순매수세 유입. 투주 물량 소화 중이나 주가 상승 모멘텀 불확실.</t>
+          <t>1.6조 규모 LNG선 등 수주 소식에도 불구하고 주가 부진 지속, 일부 목표가 상향 리포트 제시.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['연기금', '순매수', '투주']</t>
+          <t>['LNG선 수주', '목표주가', '대차']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,95 +2207,95 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83700</v>
+        <v>17090</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>343</v>
+        <v>183</v>
       </c>
       <c r="F20" t="n">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>1095</v>
+        <v>367</v>
       </c>
       <c r="H20" t="n">
-        <v>23.37</v>
+        <v>0.45</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>86200</v>
+        <v>17550</v>
       </c>
       <c r="K20" t="n">
-        <v>86200</v>
+        <v>17150</v>
       </c>
       <c r="L20" t="n">
-        <v>86300</v>
+        <v>18860</v>
       </c>
       <c r="M20" t="n">
-        <v>83500</v>
+        <v>16710</v>
       </c>
       <c r="N20" t="n">
-        <v>23.45</v>
+        <v>0.35</v>
       </c>
       <c r="O20" t="n">
-        <v>168176311650</v>
+        <v>163436415605</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>30550</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>6100</v>
       </c>
       <c r="R20" t="n">
-        <v>-140000</v>
+        <v>-12000</v>
       </c>
       <c r="S20" t="n">
-        <v>-123000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 및 경영권 참여 기대감 속에서 대미 투자 관련 단독 뉴스가 언급됨. 하지만 공매도 세력의 움직임과 투자 연기 가능성 등 부정적 요인도 혼재.</t>
+          <t>미국 보안주 상승 및 상용화, 매출 발생 기업 언급. 개미 털기 의혹 및 22,000원 목표 가격 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '대미 투자']</t>
+          <t>['보안주', '상용화', '매출 발생']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17040</v>
+        <v>83800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-2.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="F21" t="n">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="G21" t="n">
-        <v>366</v>
+        <v>1115</v>
       </c>
       <c r="H21" t="n">
-        <v>0.45</v>
+        <v>23.37</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17550</v>
+        <v>86200</v>
       </c>
       <c r="K21" t="n">
-        <v>17150</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>18860</v>
+        <v>86300</v>
       </c>
       <c r="M21" t="n">
-        <v>16710</v>
+        <v>83500</v>
       </c>
       <c r="N21" t="n">
-        <v>0.35</v>
+        <v>23.45</v>
       </c>
       <c r="O21" t="n">
-        <v>162932021345</v>
+        <v>174493490850</v>
       </c>
       <c r="P21" t="n">
-        <v>30550</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>6100</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-12000</v>
+        <v>-140000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 보안주 상승 및 상용화, 매출 발생 기업 언급. 개미 털기 의혹 및 22,000원 목표 가격 언급.</t>
+          <t>웨스팅하우스 지분 인수 및 경영권 참여 기대감 속에서 대미 투자 관련 단독 뉴스가 언급됨. 하지만 공매도 세력의 움직임과 투자 연기 가능성 등 부정적 요인도 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보안주', '상용화', '매출 발생']</t>
+          <t>['웨스팅하우스', '지분 인수', '대미 투자']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2418,13 +2418,13 @@
         <v>0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F22" t="n">
         <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="H22" t="n">
         <v>10.64</v>
@@ -2450,7 +2450,7 @@
         <v>10.53</v>
       </c>
       <c r="O22" t="n">
-        <v>69812532240</v>
+        <v>71154549000</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6050</v>
+        <v>6020</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.12%</t>
+          <t>'-4.60%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.04</v>
       </c>
       <c r="E23" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G23" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>54572992630</v>
+        <v>54929388670</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14050</v>
+        <v>13970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.21%</t>
+          <t>'-6.74%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F24" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G24" t="n">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>37817227170</v>
+        <v>38092519990</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 사우디발 호재 기대감 존재. 비축유 및 전쟁 악화 우려.</t>
+          <t>국제 유가 상승 및 전쟁 악화 우려에도 불구하고 주가 하락, 주포 이탈 가능성 및 비축유 관련 불확실성.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['국제 유가', '사우디', '비축유']</t>
+          <t>['국제유가', '전쟁', '비축유']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260916_15.xlsx
+++ b/data/trending_integrated_20260916_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G2" t="n">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>7514959170</v>
+        <v>7515343170</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -670,13 +670,13 @@
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H3" t="n">
         <v>0.4</v>
@@ -702,7 +702,7 @@
         <v>0.42</v>
       </c>
       <c r="O3" t="n">
-        <v>183705375500</v>
+        <v>183760537310</v>
       </c>
       <c r="P3" t="n">
         <v>25700</v>
@@ -762,13 +762,13 @@
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F4" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G4" t="n">
-        <v>2363</v>
+        <v>2423</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>659050697585</v>
+        <v>659256825885</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인/기관 600억 대량 순매수 및 미국 자회사 대규모 광통신 수주 기대감으로 인한 주가 상승 전망.</t>
+          <t>외인/기관 600억 대량 순매수 및 미국 자회사 대규모 광통신 수주 기대감. 4만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대량 순매수', '광통신 수주', '외인 기관']</t>
+          <t>['외인 기관 순매수', '광통신 수주', '목표가 4만원']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F5" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H5" t="n">
         <v>0.74</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>326217347464</v>
+        <v>326239397464</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광케이블 관련 미장 상승 및 4천원 지지선 언급. 단차 차익 및 알고리즘 관련 언급.</t>
+          <t>광케이블 관련주 상승 기대감 속 주가 변동성 확대. 4천원 지지선 언급 및 단기 차익 거래 시도.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광케이블', '지지선', '단차']</t>
+          <t>['광케이블', '주가 변동성', '지지선']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,10 +946,10 @@
         <v>0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
         <v>180</v>
@@ -978,7 +978,7 @@
         <v>0.84</v>
       </c>
       <c r="O6" t="n">
-        <v>132734532694</v>
+        <v>132741927319</v>
       </c>
       <c r="P6" t="n">
         <v>6190</v>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="G7" t="n">
-        <v>1904</v>
+        <v>1921</v>
       </c>
       <c r="H7" t="n">
         <v>50.2</v>
@@ -1070,7 +1070,7 @@
         <v>50.27</v>
       </c>
       <c r="O7" t="n">
-        <v>4690750325500</v>
+        <v>4695668489500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>인텔과의 미국 내 메모리 생산 방안 논의 뉴스 기반 외국인 및 기관 매수세 유입, 단기 변동성 확대 가능성.</t>
+          <t>인텔과의 미국 내 메모리 생산 협의 뉴스 기반 상승 기대. 외인 및 기관 매수세 유입 및 추세 전환 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1130,13 +1130,13 @@
         <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
         <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H8" t="n">
         <v>75.66</v>
@@ -1162,7 +1162,7 @@
         <v>75.67</v>
       </c>
       <c r="O8" t="n">
-        <v>674449183250</v>
+        <v>674800630850</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1222,10 +1222,10 @@
         <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -1254,7 +1254,7 @@
         <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>82472048820</v>
+        <v>82472836420</v>
       </c>
       <c r="P9" t="n">
         <v>10360</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>19687617930</v>
+        <v>19702270180</v>
       </c>
       <c r="P10" t="n">
         <v>19380</v>
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="G11" t="n">
-        <v>1642</v>
+        <v>1666</v>
       </c>
       <c r="H11" t="n">
         <v>46.56</v>
@@ -1438,7 +1438,7 @@
         <v>46.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2819090715750</v>
+        <v>2819715846750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 언급이 주를 이루며, 경제 전망에 대한 직접적인 내용은 부재함.</t>
+          <t>Fomc 금리 인상 우려 속에서 연말 최고점 돌파 기대감 제기. 정치적 이슈와 연계된 분석.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Fomc', '금리 인상', '연말 최고점']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1530,7 +1530,7 @@
         <v>2.68</v>
       </c>
       <c r="O12" t="n">
-        <v>67793488200</v>
+        <v>67821858470</v>
       </c>
       <c r="P12" t="n">
         <v>8980</v>
@@ -1596,7 +1596,7 @@
         <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>1.34</v>
       </c>
       <c r="O13" t="n">
-        <v>110453421591</v>
+        <v>110461430466</v>
       </c>
       <c r="P13" t="n">
         <v>5100</v>
@@ -1682,13 +1682,13 @@
         <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F14" t="n">
         <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>670</v>
+        <v>698</v>
       </c>
       <c r="H14" t="n">
         <v>3.11</v>
@@ -1714,7 +1714,7 @@
         <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>21571026772</v>
+        <v>21574909332</v>
       </c>
       <c r="P14" t="n">
         <v>16110</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
+          <t>유한양행 최대주주 보유. 제약주 특성상 단기 급등 후 하락 추세. 사기 도박판 비유 및 개미 털기 의혹.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['유한양행', '제약주', '개미 털기']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
         <v>0.67</v>
@@ -1806,7 +1806,7 @@
         <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>123166060375</v>
+        <v>123173617635</v>
       </c>
       <c r="P15" t="n">
         <v>15960</v>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미프진 관련 재료 소멸 및 도입 시점 불확실성 속에서 주가 변동성 확대 전망. 일부 투자자들은 긍정적 전망 제시.</t>
+          <t>내년 초 미프진 독점 공급 기대감에 따른 주가 상승 전망. 재료 소멸 논란 속 방향성 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1866,13 +1866,13 @@
         <v>-0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F16" t="n">
         <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H16" t="n">
         <v>26.66</v>
@@ -1898,7 +1898,7 @@
         <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>17989169730</v>
+        <v>17996708030</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1964,7 +1964,7 @@
         <v>145</v>
       </c>
       <c r="G17" t="n">
-        <v>1280</v>
+        <v>1322</v>
       </c>
       <c r="H17" t="n">
         <v>17.16</v>
@@ -1990,7 +1990,7 @@
         <v>17.5</v>
       </c>
       <c r="O17" t="n">
-        <v>10841378600</v>
+        <v>10841474300</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
+          <t>담관암, 간암 FDA 순차 승인 및 리라푸 그룹 기반 성장 기대. 유럽 신청 시점 및 FDA 실패 가능성 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA', '담관암', '신약']</t>
+          <t>['담관암', '간암', 'FDA 승인']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>1.29</v>
       </c>
       <c r="E18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F18" t="n">
         <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H18" t="n">
         <v>19.22</v>
@@ -2082,7 +2082,7 @@
         <v>17.93</v>
       </c>
       <c r="O18" t="n">
-        <v>123978325190</v>
+        <v>123997477450</v>
       </c>
       <c r="P18" t="n">
         <v>22450</v>
@@ -2142,13 +2142,13 @@
         <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F19" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="H19" t="n">
         <v>28.51</v>
@@ -2174,7 +2174,7 @@
         <v>28.9</v>
       </c>
       <c r="O19" t="n">
-        <v>45692801575</v>
+        <v>45695467975</v>
       </c>
       <c r="P19" t="n">
         <v>35350</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.6조 규모 LNG선 등 수주 소식에도 불구하고 주가 부진 지속, 일부 목표가 상향 리포트 제시.</t>
+          <t>LNG선 등 1.6조 수주 및 목표치 초과 달성. IBK 투자증권 목표주가 3만7000원 제시. 주가 하락 및 퇴출론.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LNG선 수주', '목표주가', '대차']</t>
+          <t>['LNG선 수주', '목표주가', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,7 +2234,7 @@
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F20" t="n">
         <v>105</v>
@@ -2266,7 +2266,7 @@
         <v>0.35</v>
       </c>
       <c r="O20" t="n">
-        <v>163436415605</v>
+        <v>163500400565</v>
       </c>
       <c r="P20" t="n">
         <v>30550</v>
@@ -2326,13 +2326,13 @@
         <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F21" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G21" t="n">
-        <v>1115</v>
+        <v>1139</v>
       </c>
       <c r="H21" t="n">
         <v>23.37</v>
@@ -2358,7 +2358,7 @@
         <v>23.45</v>
       </c>
       <c r="O21" t="n">
-        <v>174493490850</v>
+        <v>174499859650</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2418,13 +2418,13 @@
         <v>0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F22" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="H22" t="n">
         <v>10.64</v>
@@ -2450,7 +2450,7 @@
         <v>10.53</v>
       </c>
       <c r="O22" t="n">
-        <v>71154549000</v>
+        <v>71192580360</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>대차 해지 운동 참여 독려와 함께 주가 10만원 이상 상승 전망 언급. 대형 계약 임박 기대감도 있으나, 주가 조작 의혹 제기 및 부정적 언급도 혼재.</t>
+          <t>대차해지 운동 동참 촉구. 주가 조작 의혹 제기 및 10만원 이상 상승 전망. 대형 계약 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['대차 해지', '주가 조작', '대형 계약']</t>
+          <t>['대차해지', '주가 조작', '대형 계약']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2516,7 +2516,7 @@
         <v>63</v>
       </c>
       <c r="G23" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H23" t="n">
         <v>0.98</v>
@@ -2542,7 +2542,7 @@
         <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>54929388670</v>
+        <v>54985495070</v>
       </c>
       <c r="P23" t="n">
         <v>11370</v>
@@ -2602,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F24" t="n">
         <v>134</v>
       </c>
       <c r="G24" t="n">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>38092519990</v>
+        <v>38124972300</v>
       </c>
       <c r="P24" t="n">
         <v>36200</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>국제 유가 상승 및 전쟁 악화 우려에도 불구하고 주가 하락, 주포 이탈 가능성 및 비축유 관련 불확실성.</t>
+          <t>국제 유가 상승 및 오일 관련주 폭등 기대 속 주가 하락. 비축유 문제 및 주포 의도 불확실성.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁', '비축유']</t>
+          <t>['국제 유가', '오일 관련주', '비축유']</t>
         </is>
       </c>
       <c r="X24" t="n">
